--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2023_los_rios.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2023_los_rios.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>25.35543337070055</v>
+      </c>
+      <c r="C2">
         <v>32.54773216605278</v>
-      </c>
-      <c r="C2">
-        <v>25.35543337070055</v>
       </c>
       <c r="D2">
         <v>3.072410682557472</v>
       </c>
       <c r="E2">
-        <v>20.61246337615506</v>
+        <v>16.05758395312148</v>
       </c>
       <c r="F2">
         <v>63.32995267072346</v>
       </c>
       <c r="G2">
-        <v>16.05758395312148</v>
+        <v>20.61246337615506</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>30.21960013110456</v>
+      </c>
+      <c r="C3">
         <v>44.44444444444444</v>
-      </c>
-      <c r="C3">
-        <v>30.21960013110456</v>
       </c>
       <c r="D3">
         <v>2.25</v>
       </c>
       <c r="E3">
+        <v>17.30155751548133</v>
+      </c>
+      <c r="F3">
+        <v>57.25276787389755</v>
+      </c>
+      <c r="G3">
         <v>25.44567461062113</v>
-      </c>
-      <c r="F3">
-        <v>57.25276787389754</v>
-      </c>
-      <c r="G3">
-        <v>17.30155751548133</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>29.0115211220571</v>
+      </c>
+      <c r="C4">
         <v>36.83419602604776</v>
-      </c>
-      <c r="C4">
-        <v>29.0115211220571</v>
       </c>
       <c r="D4">
         <v>2.714868540344515</v>
       </c>
       <c r="E4">
-        <v>22.20991693934055</v>
+        <v>17.49307827837906</v>
       </c>
       <c r="F4">
         <v>60.2970047822804</v>
       </c>
       <c r="G4">
-        <v>17.49307827837906</v>
+        <v>22.20991693934055</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>28.96959459459459</v>
+      </c>
+      <c r="C5">
         <v>35.71227477477478</v>
-      </c>
-      <c r="C5">
-        <v>28.96959459459459</v>
       </c>
       <c r="D5">
         <v>2.800157666535278</v>
       </c>
       <c r="E5">
-        <v>21.68561415505599</v>
+        <v>17.59124711513805</v>
       </c>
       <c r="F5">
         <v>60.72313872980597</v>
       </c>
       <c r="G5">
-        <v>17.59124711513805</v>
+        <v>21.68561415505599</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>29.63632710468154</v>
+      </c>
+      <c r="C6">
         <v>38.21579264617239</v>
-      </c>
-      <c r="C6">
-        <v>29.63632710468154</v>
       </c>
       <c r="D6">
         <v>2.616719242902208</v>
       </c>
       <c r="E6">
-        <v>22.76753650945655</v>
+        <v>17.65621259276993</v>
       </c>
       <c r="F6">
         <v>59.57625089777353</v>
       </c>
       <c r="G6">
-        <v>17.65621259276993</v>
+        <v>22.76753650945655</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>32.00025554206862</v>
+      </c>
+      <c r="C7">
         <v>31.94275857663068</v>
-      </c>
-      <c r="C7">
-        <v>32.00025554206862</v>
       </c>
       <c r="D7">
         <v>3.1306</v>
       </c>
       <c r="E7">
+        <v>19.51913334892059</v>
+      </c>
+      <c r="F7">
+        <v>60.9968046138259</v>
+      </c>
+      <c r="G7">
         <v>19.48406203725353</v>
-      </c>
-      <c r="F7">
-        <v>60.99680461382589</v>
-      </c>
-      <c r="G7">
-        <v>19.51913334892058</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>28.34685234369392</v>
+      </c>
+      <c r="C8">
         <v>37.84365802885651</v>
-      </c>
-      <c r="C8">
-        <v>28.34685234369392</v>
       </c>
       <c r="D8">
         <v>2.642450682852807</v>
       </c>
       <c r="E8">
-        <v>22.77125086385626</v>
+        <v>17.05684174153421</v>
       </c>
       <c r="F8">
         <v>60.17190739460954</v>
       </c>
       <c r="G8">
-        <v>17.05684174153421</v>
+        <v>22.77125086385626</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>29.18372075063711</v>
+      </c>
+      <c r="C9">
         <v>33.80183797976678</v>
-      </c>
-      <c r="C9">
-        <v>29.18372075063711</v>
       </c>
       <c r="D9">
         <v>2.958419008453279</v>
       </c>
       <c r="E9">
-        <v>20.73916133617626</v>
+        <v>17.90570954750059</v>
       </c>
       <c r="F9">
         <v>61.35512911632314</v>
       </c>
       <c r="G9">
-        <v>17.90570954750059</v>
+        <v>20.73916133617626</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>27.67084106369821</v>
+      </c>
+      <c r="C10">
         <v>37.85946196660483</v>
-      </c>
-      <c r="C10">
-        <v>27.67084106369821</v>
       </c>
       <c r="D10">
         <v>2.641347626339969</v>
       </c>
       <c r="E10">
-        <v>22.87162004389856</v>
+        <v>16.71648064260029</v>
       </c>
       <c r="F10">
-        <v>60.41189931350113</v>
+        <v>60.41189931350115</v>
       </c>
       <c r="G10">
-        <v>16.71648064260028</v>
+        <v>22.87162004389857</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>30.73514784338548</v>
+      </c>
+      <c r="C11">
         <v>34.08083913554571</v>
-      </c>
-      <c r="C11">
-        <v>30.73514784338548</v>
       </c>
       <c r="D11">
         <v>2.934200053064473</v>
       </c>
       <c r="E11">
-        <v>20.67811488451198</v>
+        <v>18.64815932407966</v>
       </c>
       <c r="F11">
         <v>60.67372579140835</v>
       </c>
       <c r="G11">
-        <v>18.64815932407966</v>
+        <v>20.67811488451198</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>28.80741337630943</v>
+      </c>
+      <c r="C12">
         <v>37.79210314262691</v>
-      </c>
-      <c r="C12">
-        <v>28.80741337630943</v>
       </c>
       <c r="D12">
         <v>2.646055437100213</v>
       </c>
       <c r="E12">
+        <v>17.29141475211608</v>
+      </c>
+      <c r="F12">
+        <v>60.0241837968561</v>
+      </c>
+      <c r="G12">
         <v>22.68440145102781</v>
-      </c>
-      <c r="F12">
-        <v>60.02418379685611</v>
-      </c>
-      <c r="G12">
-        <v>17.29141475211608</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>34.5697851860547</v>
+      </c>
+      <c r="C13">
         <v>22.12701021246625</v>
-      </c>
-      <c r="C13">
-        <v>34.5697851860547</v>
       </c>
       <c r="D13">
         <v>4.519363395225464</v>
       </c>
       <c r="E13">
-        <v>14.12090793317852</v>
+        <v>22.06157764626564</v>
       </c>
       <c r="F13">
         <v>63.81751442055585</v>
       </c>
       <c r="G13">
-        <v>22.06157764626564</v>
+        <v>14.12090793317852</v>
       </c>
     </row>
   </sheetData>
